--- a/OT_convert.xlsx
+++ b/OT_convert.xlsx
@@ -14,21 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
-    <t>9</t>
+    <t>A049</t>
   </si>
   <si>
-    <t>2021-10-01</t>
+    <t>2021-01-20</t>
   </si>
   <si>
-    <t>2021-10-02</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>2021-01-19</t>
   </si>
 </sst>
 </file>
@@ -360,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -368,7 +362,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -383,50 +377,6 @@
       </c>
       <c r="C2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1.5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/OT_convert.xlsx
+++ b/OT_convert.xlsx
@@ -11,20 +11,6 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
-  <si>
-    <t>A049</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,32 +340,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>